--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128054566</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Buxåsen, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334028</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6498683</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundals-Ryr</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128054566</v>
       </c>
       <c r="B4" t="n">
-        <v>95891</v>
+        <v>95903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31985-2025 artfynd.xlsx
+++ b/artfynd/A 31985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2189458</v>
+        <v>128054566</v>
       </c>
       <c r="B2" t="n">
-        <v>104489</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlsmyr, 1 km N om Ideström, Dls</t>
+          <t>Buxåsen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334260.7585158044</v>
+        <v>334028</v>
       </c>
       <c r="R2" t="n">
-        <v>6499496.186889985</v>
+        <v>6498683</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1978-05-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1978-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hasselsnår</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3771622</v>
+        <v>128054567</v>
       </c>
       <c r="B3" t="n">
-        <v>103177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlsmyr, 1 km N om Ideström, Dls</t>
+          <t>Buxåsen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334260.7585158044</v>
+        <v>333872</v>
       </c>
       <c r="R3" t="n">
-        <v>6499496.186889985</v>
+        <v>6498516</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1978-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1978-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,31 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>torprest</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128054566</v>
+        <v>2189458</v>
       </c>
       <c r="B4" t="n">
-        <v>95903</v>
+        <v>107609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Buxåsen, Dls</t>
+          <t>Karlsmyr, 1 km N om Ideström, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334028</v>
+        <v>334261</v>
       </c>
       <c r="R4" t="n">
-        <v>6498683</v>
+        <v>6499496</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>1978-05-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>1978-05-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,19 +950,126 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>hasselsnår</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3771622</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karlsmyr, 1 km N om Ideström, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334261</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6499496</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundals-Ryr</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1978-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1978-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>torprest</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
